--- a/BVL-base-datos.xlsx
+++ b/BVL-base-datos.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPACASC1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CVERDEC1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FERREYC1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNACEMC1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNJUANC1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UNACEMC1" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -608,23 +609,48 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>SNJUANC1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1T2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1T2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>UNACEMC1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>UNACEM CORP S.A.A.</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>7</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>3T2024</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1T2026</t>
         </is>
@@ -8446,6 +8472,602 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:W6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bolsa de valores</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Trimestre</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fuente del balance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>URL del documento</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro del trimestre (M PEN)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Volumen de ventas (M PEN)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Nivel de endeudamiento (Pasivos/Activos)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ROE trimestral (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>EBIT (M PEN)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>EBITDA (M PEN)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Moneda</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Notas metodológicas</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_corrida</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_eeff</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>archivo_local</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>activos_M</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pasivos_M</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>patrimonio_M</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>deuda_financiera_M</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>caja_M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>313.68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8124</v>
+      </c>
+      <c r="K2" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="L2" t="n">
+        <v>149.58</v>
+      </c>
+      <c r="M2" t="n">
+        <v>154.29</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2026_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1475.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1198.62</v>
+      </c>
+      <c r="U2" t="n">
+        <v>276.86</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="W2" t="n">
+        <v>182.23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRIMESTRE IV</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="I3" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5288</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="L3" t="n">
+        <v>188.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>210.08</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIV.xlsx</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1361.18</v>
+      </c>
+      <c r="T3" t="n">
+        <v>719.77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>641.41</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>322.13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRIMESTRE III</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>169.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>185.49</v>
+      </c>
+      <c r="M4" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREIII.xlsx</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1523.43</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1035.81</v>
+      </c>
+      <c r="U4" t="n">
+        <v>487.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="W4" t="n">
+        <v>203.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRIMESTRE II</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="K5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>137.12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>148.73</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREII.xlsx</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1330.76</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1012.7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="W5" t="n">
+        <v>162.53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CERVECERIA SAN JUAN S.A.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BVL (Bolsa de Valores de Lima)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRIMESTRE I</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SMV — Superintendencia del Mercado de Valores</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.smv.gob.pe/SIMV/Frm_InformacionFinancieraPorPeriodo?data=16BF4C8EF499F678B5AE402C1CFE8FC16710365A6C</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>275.79</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>98.22</v>
+      </c>
+      <c r="M6" t="n">
+        <v>104.24</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Montos en millones de PEN (SMV reporta en miles). ROE trimestral = utilidad del trimestre / patrimonio, NO anualizado. EBIT aproximado desde líneas operativas del Estado de Resultados. EBITDA = EBIT + D&amp;A del flujo de efectivo. EEFF Consolidada.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Consolidada</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>/Users/sebastianportocarrerohuanca/stock-analyst-data/SMV_CERVECERIA_SAN_JUAN_S_A__2025_TRIMESTREI.xlsx</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1346.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1138.13</v>
+      </c>
+      <c r="U6" t="n">
+        <v>208.02</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>223.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
